--- a/examples/Temozolomide/CEREBRO_X_Completed_Data_Temozolomide.xlsx
+++ b/examples/Temozolomide/CEREBRO_X_Completed_Data_Temozolomide.xlsx
@@ -4374,7 +4374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-05T08:09:24Z  | Pipeline: v20  | Source: CEREBRO_Input_Temozolomide.xlsx</t>
+          <t>Generated: 2026-09-05T18:10:59Z  | Pipeline: v20  | Source: CEREBRO_Input_Temozolomide.xlsx</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>81.66</v>
+        <v>81.72</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>80.08</v>
+        <v>80.14</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>78.59999999999999</v>
+        <v>78.66</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="C26" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="F26" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 47.5 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 50.0 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="F40" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 25.0 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 27.5 NEEDS REVIEW. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -9549,11 +9549,11 @@
         </is>
       </c>
       <c r="D5" s="8" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>70.48</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -9801,11 +9801,11 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -10233,11 +10233,11 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>64.3</v>
+        <v>65.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -11608,11 +11608,11 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>70.48</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -11716,11 +11716,11 @@
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -13365,7 +13365,7 @@
         <v>1</v>
       </c>
       <c r="AN4" s="28" t="n">
-        <v>81.66</v>
+        <v>81.72</v>
       </c>
       <c r="AO4" s="28" t="n">
         <v>81.64</v>
@@ -13374,7 +13374,7 @@
         <v>58.39</v>
       </c>
       <c r="AQ4" s="28" t="n">
-        <v>79.95</v>
+        <v>80.33</v>
       </c>
       <c r="AR4" s="28" t="n">
         <v>93.65000000000001</v>
@@ -13383,7 +13383,7 @@
         <v>61.67</v>
       </c>
       <c r="AT4" s="28" t="n">
-        <v>81.31</v>
+        <v>81.44</v>
       </c>
       <c r="AU4" s="28" t="n">
         <v>67.02</v>
@@ -13400,7 +13400,7 @@
         </is>
       </c>
       <c r="AY4" s="28" t="n">
-        <v>77.77</v>
+        <v>77.83</v>
       </c>
       <c r="AZ4" s="28" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>80.08</v>
+        <v>80.14</v>
       </c>
       <c r="AO5" t="n">
         <v>80.65000000000001</v>
@@ -13615,7 +13615,7 @@
         <v>54.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>77</v>
+        <v>77.37</v>
       </c>
       <c r="AR5" t="n">
         <v>93.73</v>
@@ -13624,7 +13624,7 @@
         <v>56.67</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.48</v>
+        <v>73.62</v>
       </c>
       <c r="AU5" t="n">
         <v>70.31</v>
@@ -13641,7 +13641,7 @@
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>76.27</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>3</v>
       </c>
       <c r="AN6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.66</v>
       </c>
       <c r="AO6" t="n">
         <v>82.3</v>
@@ -13856,7 +13856,7 @@
         <v>55.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>58.93</v>
+        <v>59.31</v>
       </c>
       <c r="AR6" t="n">
         <v>92.28</v>
@@ -13865,7 +13865,7 @@
         <v>65</v>
       </c>
       <c r="AT6" t="n">
-        <v>66.38</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="AU6" t="n">
         <v>68.75</v>
@@ -13882,7 +13882,7 @@
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>74.86</v>
+        <v>74.92</v>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>78.34999999999999</v>
+        <v>78.41</v>
       </c>
       <c r="AO7" t="n">
         <v>81.31999999999999</v>
@@ -14097,7 +14097,7 @@
         <v>55.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>58.93</v>
+        <v>59.31</v>
       </c>
       <c r="AR7" t="n">
         <v>92.8</v>
@@ -14106,7 +14106,7 @@
         <v>65</v>
       </c>
       <c r="AT7" t="n">
-        <v>69.27</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AU7" t="n">
         <v>67.95999999999999</v>
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>74.62</v>
+        <v>74.67</v>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>75.51000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="AO8" t="n">
         <v>78.92</v>
@@ -14338,7 +14338,7 @@
         <v>67.09</v>
       </c>
       <c r="AQ8" t="n">
-        <v>62.54</v>
+        <v>62.92</v>
       </c>
       <c r="AR8" t="n">
         <v>94.79000000000001</v>
@@ -14347,7 +14347,7 @@
         <v>60</v>
       </c>
       <c r="AT8" t="n">
-        <v>66.64</v>
+        <v>66.78</v>
       </c>
       <c r="AU8" t="n">
         <v>66.88</v>
@@ -14364,7 +14364,7 @@
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>75.51000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>6</v>
       </c>
       <c r="AN9" t="n">
-        <v>74.65000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AO9" t="n">
         <v>81.38</v>
@@ -14579,7 +14579,7 @@
         <v>67.09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>58.03</v>
+        <v>58.41</v>
       </c>
       <c r="AR9" t="n">
         <v>92.68000000000001</v>
@@ -14588,7 +14588,7 @@
         <v>55</v>
       </c>
       <c r="AT9" t="n">
-        <v>69.98</v>
+        <v>70.12</v>
       </c>
       <c r="AU9" t="n">
         <v>67.19</v>
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>74.65000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>74.59</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AO10" t="n">
         <v>64.7</v>
@@ -14820,7 +14820,7 @@
         <v>58.39</v>
       </c>
       <c r="AQ10" t="n">
-        <v>79.95</v>
+        <v>80.33</v>
       </c>
       <c r="AR10" t="n">
         <v>95.48</v>
@@ -14829,7 +14829,7 @@
         <v>60.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>80.76000000000001</v>
+        <v>80.89</v>
       </c>
       <c r="AU10" t="n">
         <v>67.19</v>
@@ -14846,7 +14846,7 @@
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>71.04000000000001</v>
+        <v>71.09</v>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>62.16</v>
+        <v>62.21</v>
       </c>
       <c r="AO11" t="n">
         <v>59.05</v>
@@ -15061,7 +15061,7 @@
         <v>67.09</v>
       </c>
       <c r="AQ11" t="n">
-        <v>62.54</v>
+        <v>62.92</v>
       </c>
       <c r="AR11" t="n">
         <v>94.56999999999999</v>
@@ -15070,7 +15070,7 @@
         <v>39.13</v>
       </c>
       <c r="AT11" t="n">
-        <v>65.76000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="AU11" t="n">
         <v>65</v>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>65.43000000000001</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>81.66</v>
+        <v>81.72</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>81.64</v>
@@ -15608,8 +15608,8 @@
       <c r="E5" s="31" t="n">
         <v>58.39</v>
       </c>
-      <c r="F5" s="32" t="n">
-        <v>79.95</v>
+      <c r="F5" s="30" t="n">
+        <v>80.33</v>
       </c>
       <c r="G5" s="30" t="n">
         <v>93.65000000000001</v>
@@ -15618,13 +15618,13 @@
         <v>61.67</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>81.31</v>
+        <v>81.44</v>
       </c>
       <c r="J5" s="32" t="n">
         <v>67.02</v>
       </c>
       <c r="K5" s="32" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="L5" s="30" t="n">
         <v>100</v>
@@ -15645,7 +15645,7 @@
         <v>100</v>
       </c>
       <c r="R5" s="32" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="S5" s="30" t="n">
         <v>100</v>
@@ -15681,7 +15681,7 @@
         <v>100</v>
       </c>
       <c r="AD5" s="32" t="n">
-        <v>64.3</v>
+        <v>65.5</v>
       </c>
       <c r="AE5" s="32" t="n">
         <v>65.92</v>
@@ -15805,7 +15805,7 @@
         </is>
       </c>
       <c r="C6" s="28" t="n">
-        <v>80.08</v>
+        <v>80.14</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>80.65000000000001</v>
@@ -15814,7 +15814,7 @@
         <v>54.5</v>
       </c>
       <c r="F6" s="32" t="n">
-        <v>77</v>
+        <v>77.37</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>93.73</v>
@@ -15823,13 +15823,13 @@
         <v>56.67</v>
       </c>
       <c r="I6" s="32" t="n">
-        <v>73.48</v>
+        <v>73.62</v>
       </c>
       <c r="J6" s="32" t="n">
         <v>70.31</v>
       </c>
       <c r="K6" s="32" t="n">
-        <v>62.4</v>
+        <v>62.14</v>
       </c>
       <c r="L6" s="30" t="n">
         <v>100</v>
@@ -15850,7 +15850,7 @@
         <v>80</v>
       </c>
       <c r="R6" s="31" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="S6" s="30" t="n">
         <v>100</v>
@@ -15886,7 +15886,7 @@
         <v>100</v>
       </c>
       <c r="AD6" s="32" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="AE6" s="32" t="n">
         <v>74.08</v>
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="C7" s="35" t="n">
-        <v>78.59999999999999</v>
+        <v>78.66</v>
       </c>
       <c r="D7" s="30" t="n">
         <v>82.3</v>
@@ -16019,7 +16019,7 @@
         <v>55.27</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>58.93</v>
+        <v>59.31</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>92.28</v>
@@ -16028,13 +16028,13 @@
         <v>65</v>
       </c>
       <c r="I7" s="32" t="n">
-        <v>66.38</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="J7" s="32" t="n">
         <v>68.75</v>
       </c>
       <c r="K7" s="32" t="n">
-        <v>60.85</v>
+        <v>60.6</v>
       </c>
       <c r="L7" s="30" t="n">
         <v>100</v>
@@ -16055,7 +16055,7 @@
         <v>100</v>
       </c>
       <c r="R7" s="34" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="S7" s="30" t="n">
         <v>100</v>
@@ -16091,7 +16091,7 @@
         <v>80</v>
       </c>
       <c r="AD7" s="32" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="AE7" s="32" t="n">
         <v>61.16</v>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="C8" s="35" t="n">
-        <v>78.34999999999999</v>
+        <v>78.41</v>
       </c>
       <c r="D8" s="30" t="n">
         <v>81.31999999999999</v>
@@ -16224,7 +16224,7 @@
         <v>55.05</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>58.93</v>
+        <v>59.31</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>92.8</v>
@@ -16233,13 +16233,13 @@
         <v>65</v>
       </c>
       <c r="I8" s="32" t="n">
-        <v>69.27</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J8" s="32" t="n">
         <v>67.95999999999999</v>
       </c>
       <c r="K8" s="32" t="n">
-        <v>60.85</v>
+        <v>60.6</v>
       </c>
       <c r="L8" s="30" t="n">
         <v>100</v>
@@ -16260,7 +16260,7 @@
         <v>100</v>
       </c>
       <c r="R8" s="34" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="S8" s="30" t="n">
         <v>100</v>
@@ -16296,7 +16296,7 @@
         <v>100</v>
       </c>
       <c r="AD8" s="32" t="n">
-        <v>76.3</v>
+        <v>77.5</v>
       </c>
       <c r="AE8" s="32" t="n">
         <v>65.38</v>
@@ -16420,7 +16420,7 @@
         </is>
       </c>
       <c r="C9" s="35" t="n">
-        <v>75.51000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>78.92</v>
@@ -16429,7 +16429,7 @@
         <v>67.09</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>62.54</v>
+        <v>62.92</v>
       </c>
       <c r="G9" s="30" t="n">
         <v>94.79000000000001</v>
@@ -16438,13 +16438,13 @@
         <v>60</v>
       </c>
       <c r="I9" s="32" t="n">
-        <v>66.64</v>
+        <v>66.78</v>
       </c>
       <c r="J9" s="32" t="n">
         <v>66.88</v>
       </c>
       <c r="K9" s="31" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="L9" s="30" t="n">
         <v>100</v>
@@ -16465,7 +16465,7 @@
         <v>80</v>
       </c>
       <c r="R9" s="31" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="S9" s="30" t="n">
         <v>100</v>
@@ -16501,7 +16501,7 @@
         <v>100</v>
       </c>
       <c r="AD9" s="32" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="AE9" s="30" t="n">
         <v>87.52</v>
@@ -16625,7 +16625,7 @@
         </is>
       </c>
       <c r="C10" s="35" t="n">
-        <v>74.65000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="D10" s="30" t="n">
         <v>81.38</v>
@@ -16634,7 +16634,7 @@
         <v>67.09</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>58.03</v>
+        <v>58.41</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>92.68000000000001</v>
@@ -16643,13 +16643,13 @@
         <v>55</v>
       </c>
       <c r="I10" s="32" t="n">
-        <v>69.98</v>
+        <v>70.12</v>
       </c>
       <c r="J10" s="32" t="n">
         <v>67.19</v>
       </c>
       <c r="K10" s="31" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="L10" s="30" t="n">
         <v>100</v>
@@ -16669,8 +16669,8 @@
       <c r="Q10" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="R10" s="33" t="n">
-        <v>17.5</v>
+      <c r="R10" s="34" t="n">
+        <v>20</v>
       </c>
       <c r="S10" s="30" t="n">
         <v>100</v>
@@ -16705,8 +16705,8 @@
       <c r="AC10" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="AD10" s="32" t="n">
-        <v>79.3</v>
+      <c r="AD10" s="30" t="n">
+        <v>80.5</v>
       </c>
       <c r="AE10" s="30" t="n">
         <v>81.87</v>
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="C11" s="35" t="n">
-        <v>74.59</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="D11" s="32" t="n">
         <v>64.7</v>
@@ -16838,8 +16838,8 @@
       <c r="E11" s="31" t="n">
         <v>58.39</v>
       </c>
-      <c r="F11" s="32" t="n">
-        <v>79.95</v>
+      <c r="F11" s="30" t="n">
+        <v>80.33</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>95.48</v>
@@ -16848,13 +16848,13 @@
         <v>60.6</v>
       </c>
       <c r="I11" s="30" t="n">
-        <v>80.76000000000001</v>
+        <v>80.89</v>
       </c>
       <c r="J11" s="32" t="n">
         <v>67.19</v>
       </c>
       <c r="K11" s="32" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="L11" s="30" t="n">
         <v>100</v>
@@ -16875,7 +16875,7 @@
         <v>70</v>
       </c>
       <c r="R11" s="32" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="S11" s="30" t="n">
         <v>100</v>
@@ -16910,8 +16910,8 @@
       <c r="AC11" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="AD11" s="32" t="n">
-        <v>79.3</v>
+      <c r="AD11" s="30" t="n">
+        <v>80.5</v>
       </c>
       <c r="AE11" s="30" t="n">
         <v>80.52</v>
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="C12" s="35" t="n">
-        <v>62.16</v>
+        <v>62.21</v>
       </c>
       <c r="D12" s="31" t="n">
         <v>59.05</v>
@@ -17044,7 +17044,7 @@
         <v>67.09</v>
       </c>
       <c r="F12" s="32" t="n">
-        <v>62.54</v>
+        <v>62.92</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>94.56999999999999</v>
@@ -17053,13 +17053,13 @@
         <v>39.13</v>
       </c>
       <c r="I12" s="32" t="n">
-        <v>65.76000000000001</v>
+        <v>65.89</v>
       </c>
       <c r="J12" s="32" t="n">
         <v>65</v>
       </c>
       <c r="K12" s="31" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="L12" s="30" t="n">
         <v>100</v>
@@ -17080,7 +17080,7 @@
         <v>50</v>
       </c>
       <c r="R12" s="31" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="S12" s="30" t="n">
         <v>100</v>
@@ -17115,8 +17115,8 @@
       <c r="AC12" s="30" t="n">
         <v>80</v>
       </c>
-      <c r="AD12" s="32" t="n">
-        <v>79.3</v>
+      <c r="AD12" s="30" t="n">
+        <v>80.5</v>
       </c>
       <c r="AE12" s="30" t="n">
         <v>95.12</v>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 81/100  G2_Release_Kinetics: 54/100  G3_Stability: 77/100  G4_Safety: 94/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 73/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 81/100  G2_Release_Kinetics: 54/100  G3_Stability: 77/100  G4_Safety: 94/100  G5_Glymphatic_BBB: 57/100  G6_Manufacturability: 74/100  G7_DrugDDS_Fit: 70/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>78.6 / 100</t>
+          <t>78.7 / 100</t>
         </is>
       </c>
       <c r="D24" s="35" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>RVG29-Liposome-pH: composite CNS-principle score = 78.6/100 (GOOD). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (92.3/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>RVG29-Liposome-pH: composite CNS-principle score = 78.7/100 (GOOD). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: RVG29. Strongest group: G4 Safety (92.3/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17603,7 +17603,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>G1_CNS_Delivery: 82/100  G2_Release_Kinetics: 55/100  G3_Stability: 59/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 66/100  G7_DrugDDS_Fit: 69/100  G8_Translational: 0/100</t>
+          <t>G1_CNS_Delivery: 82/100  G2_Release_Kinetics: 55/100  G3_Stability: 59/100  G4_Safety: 92/100  G5_Glymphatic_BBB: 65/100  G6_Manufacturability: 67/100  G7_DrugDDS_Fit: 69/100  G8_Translational: 0/100</t>
         </is>
       </c>
     </row>
@@ -17659,34 +17659,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>27.1/100</t>
+          <t>27.5/100</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>27.1/100</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
         </is>
       </c>
     </row>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>78.3 / 100</t>
+          <t>78.4 / 100</t>
         </is>
       </c>
       <c r="D34" s="35" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Tf-PEG-Liposome: composite CNS-principle score = 78.3/100 (GOOD). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (92.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Tf-PEG-Liposome: composite CNS-principle score = 78.4/100 (GOOD). Carrier: liposome, size 0.0 nm, ζ +0.0 mV, ligand: Transferrin. Strongest group: G4 Safety (92.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -17805,34 +17805,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>27.1/100</t>
+          <t>27.5/100</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>27.1/100</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
         </is>
       </c>
     </row>
@@ -17866,7 +17866,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>75.5 / 100</t>
+          <t>75.6 / 100</t>
         </is>
       </c>
       <c r="D44" s="35" t="inlineStr">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>ApoE-LNP: composite CNS-principle score = 75.5/100 (GOOD). Carrier: lnp, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (94.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>ApoE-LNP: composite CNS-principle score = 75.6/100 (GOOD). Carrier: lnp, size 0.0 nm, ζ +0.0 mV, ligand: ApoE. Strongest group: G4 Safety (94.8/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>Lf-Polymer-Micelle: composite CNS-principle score = 74.6/100 (GOOD). Carrier: micelle, size 0.0 nm, ζ +0.0 mV, ligand: Lactoferrin. Strongest group: G4 Safety (92.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
+          <t>Lf-Polymer-Micelle: composite CNS-principle score = 74.7/100 (GOOD). Carrier: micelle, size 0.0 nm, ζ +0.0 mV, ligand: Lactoferrin. Strongest group: G4 Safety (92.7/100); weakest: G8 Translational (0.0/100). Evaluated against all 57 Class A surrogate principles.</t>
         </is>
       </c>
     </row>
@@ -18097,34 +18097,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18.1/100</t>
+          <t>20.0/100</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>18.1/100</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> — Hint: Below 60. Method: Arrhenius k=A·exp(-Ea/RT) for carrier; minus penalties for dru</t>
+          <t xml:space="preserve"> — Hint: Below 60. Method: log10(crit_shear/operating_shear) × 30; crit_shear softened by</t>
         </is>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>74.6 / 100</t>
+          <t>74.7 / 100</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -18611,11 +18611,11 @@
         </is>
       </c>
       <c r="E5" s="41" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>70.48</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -18898,11 +18898,11 @@
         </is>
       </c>
       <c r="E12" s="41" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -19390,11 +19390,11 @@
         </is>
       </c>
       <c r="E24" s="41" t="n">
-        <v>64.3</v>
+        <v>65.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -20948,11 +20948,11 @@
         </is>
       </c>
       <c r="E62" s="41" t="n">
-        <v>62.4</v>
+        <v>62.14</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>62.14</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -21235,11 +21235,11 @@
         </is>
       </c>
       <c r="E69" s="8" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
@@ -21727,11 +21727,11 @@
         </is>
       </c>
       <c r="E81" s="41" t="n">
-        <v>73.3</v>
+        <v>74.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
@@ -23285,11 +23285,11 @@
         </is>
       </c>
       <c r="E119" s="41" t="n">
-        <v>60.85</v>
+        <v>60.6</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
@@ -23572,11 +23572,11 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -24064,11 +24064,11 @@
         </is>
       </c>
       <c r="E138" s="41" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -25622,11 +25622,11 @@
         </is>
       </c>
       <c r="E176" s="41" t="n">
-        <v>60.85</v>
+        <v>60.6</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>60.85</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -25909,11 +25909,11 @@
         </is>
       </c>
       <c r="E183" s="9" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
@@ -26401,11 +26401,11 @@
         </is>
       </c>
       <c r="E195" s="41" t="n">
-        <v>76.3</v>
+        <v>77.5</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
@@ -27959,11 +27959,11 @@
         </is>
       </c>
       <c r="E233" s="8" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.26</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
@@ -28246,11 +28246,11 @@
         </is>
       </c>
       <c r="E240" s="8" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
@@ -28738,11 +28738,11 @@
         </is>
       </c>
       <c r="E252" s="41" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
@@ -30296,11 +30296,11 @@
         </is>
       </c>
       <c r="E290" s="8" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.26</t>
         </is>
       </c>
       <c r="G290" s="5" t="inlineStr">
@@ -30582,12 +30582,12 @@
           <t>Degradation Kinetics Under Oxidative Stress</t>
         </is>
       </c>
-      <c r="E297" s="42" t="n">
-        <v>17.5</v>
+      <c r="E297" s="9" t="n">
+        <v>20</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G297" s="5" t="inlineStr">
@@ -31074,12 +31074,12 @@
           <t>Cost-Efficiency Engine</t>
         </is>
       </c>
-      <c r="E309" s="41" t="n">
-        <v>79.3</v>
+      <c r="E309" s="7" t="n">
+        <v>80.5</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G309" s="5" t="inlineStr">
@@ -32633,11 +32633,11 @@
         </is>
       </c>
       <c r="E347" s="41" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>70.73</t>
+          <t>70.48</t>
         </is>
       </c>
       <c r="G347" s="5" t="inlineStr">
@@ -32920,11 +32920,11 @@
         </is>
       </c>
       <c r="E354" s="41" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="G354" s="5" t="inlineStr">
@@ -33411,12 +33411,12 @@
           <t>Cost-Efficiency Engine</t>
         </is>
       </c>
-      <c r="E366" s="41" t="n">
-        <v>79.3</v>
+      <c r="E366" s="7" t="n">
+        <v>80.5</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G366" s="5" t="inlineStr">
@@ -34970,11 +34970,11 @@
         </is>
       </c>
       <c r="E404" s="8" t="n">
-        <v>57.52</v>
+        <v>57.26</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.26</t>
         </is>
       </c>
       <c r="G404" s="5" t="inlineStr">
@@ -35257,11 +35257,11 @@
         </is>
       </c>
       <c r="E411" s="8" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="G411" s="5" t="inlineStr">
@@ -35748,12 +35748,12 @@
           <t>Cost-Efficiency Engine</t>
         </is>
       </c>
-      <c r="E423" s="41" t="n">
-        <v>79.3</v>
+      <c r="E423" s="7" t="n">
+        <v>80.5</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="G423" s="5" t="inlineStr">
@@ -37430,10 +37430,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="D10" t="n">
-        <v>70.73</v>
+        <v>70.48</v>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Full MD stress simulation: surrogate score 70.73 PASSED. Full deep simulation requires external HPC.</t>
+          <t>Full MD stress simulation: surrogate score 70.48 PASSED. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
@@ -37547,10 +37547,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="D13" t="n">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
@@ -37570,7 +37570,7 @@
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Full radical-chain reaction MD: surrogate score 70.0 PASSED. Full deep simulation requires external HPC.</t>
+          <t>Full radical-chain reaction MD: surrogate score 72.5 PASSED. Full deep simulation requires external HPC.</t>
         </is>
       </c>
     </row>
